--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:49</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:53</t>
+    <t xml:space="preserve">2026-09-24 00:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:31</t>
+    <t xml:space="preserve">2026-09-27 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11.69</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.52</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.93</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.77</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.44</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.33</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.46</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.76</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3.22</v>
+        <v>-32.15</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-7.55</v>
+        <v>-75.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-10-01 21:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 21:00</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-04 08:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:20</t>
+    <t xml:space="preserve">2026-10-05 08:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
